--- a/data/trans_orig/P1422-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2012</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1951</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>452195</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>454146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>428273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>430230</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882420</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>884376</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,47 +1110,47 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t>5179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681797</t>
+          <t>681900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>608207</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>610255</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1292142</t>
+          <t>1292163</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2939</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16649</t>
+          <t>16567</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>3724</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15965</t>
+          <t>17862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665214</t>
+          <t>665296</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678924</t>
+          <t>678115</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>707531</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>709574</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1375472</t>
+          <t>1373575</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1388488</t>
+          <t>1387713</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13218</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4986</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18233</t>
+          <t>18103</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604236</t>
+          <t>604374</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613579</t>
+          <t>613592</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601046</t>
+          <t>600897</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>612203</t>
+          <t>611319</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1210647</t>
+          <t>1210777</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1223894</t>
+          <t>1223786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6972</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7897</t>
+          <t>9746</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422451</t>
+          <t>422457</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>443036</t>
+          <t>442074</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>869332</t>
+          <t>867483</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876292</t>
+          <t>876289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>2030</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12637</t>
+          <t>12655</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,82 +2462,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6167</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2988</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13364</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,78%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>12048</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>6078</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>20132</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>6167</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2115</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>12435</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,51%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>12048</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>6143</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>21053</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297149</t>
+          <t>297131</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>306943</t>
+          <t>307756</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,82 +2575,82 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>99,34%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>347829</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>340632</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>351008</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>98,26%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>96,22%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>614</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>651734</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>643650</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>657704</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>98,18%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>96,97%</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
           <t>99,08%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>347829</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>341561</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>351881</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>96,49%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>651734</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>642729</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>657639</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>98,18%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,82 +2805,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9,88%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>12153</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>6220</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>20981</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>3,12%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>5,39%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>25019</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>16725</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>39293</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
           <t>2,62%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>12153</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>6441</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>21114</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>5,43%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>25019</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>15745</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>37591</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>2,46%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>226481</t>
+          <t>225157</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243317</t>
+          <t>243386</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,82 +2918,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>376826</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>367998</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>382759</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>96,88%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>94,61%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>551</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>613811</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>599537</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>622105</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>96,08%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>93,85%</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
           <t>97,38%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>339</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>376826</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>367865</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>382538</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>96,88%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>551</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>613811</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>601239</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>623085</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>94,12%</t>
-        </is>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
-        <is>
-          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23305</t>
+          <t>23652</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37056</t>
+          <t>37842</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>44325</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76057</t>
+          <t>76054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3376870</t>
+          <t>3378058</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3403474</t>
+          <t>3403127</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3518042</t>
+          <t>3517256</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3538481</t>
+          <t>3538501</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6905820</t>
+          <t>6905823</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6937863</t>
+          <t>6937552</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2016</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,97 +3711,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2044</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1876</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417419</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>419463</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>393879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>395755</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>813256</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>815218</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,62 +4089,62 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>5515</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>4901</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>584527</t>
+          <t>585575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>561678</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>563544</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1149139</t>
+          <t>1148525</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6467</t>
+          <t>5593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,47 +4432,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1846</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1846</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>662630</t>
+          <t>663504</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>659479</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>661386</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1323987</t>
+          <t>1323993</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1891</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7038</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2966</t>
+          <t>2987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13195</t>
+          <t>14077</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635035</t>
+          <t>635320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644157</t>
+          <t>644166</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>641793</t>
+          <t>642039</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1281930</t>
+          <t>1281048</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1292159</t>
+          <t>1292138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>10879</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>469879</t>
+          <t>469987</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>488916</t>
+          <t>490470</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>963727</t>
+          <t>963888</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>973640</t>
+          <t>973636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2726</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13886</t>
+          <t>14249</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2811</t>
+          <t>2774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23449</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320444</t>
+          <t>320081</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331604</t>
+          <t>331522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>362587</t>
+          <t>362842</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>374951</t>
+          <t>374988</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>688643</t>
+          <t>687847</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>704858</t>
+          <t>704366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>1693</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10027</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>4469</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19367</t>
+          <t>19187</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7912</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25353</t>
+          <t>25222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246971</t>
+          <t>246536</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255332</t>
+          <t>255305</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380802</t>
+          <t>380982</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>396453</t>
+          <t>395700</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>631814</t>
+          <t>631945</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649773</t>
+          <t>649255</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32003</t>
+          <t>32006</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12388</t>
+          <t>12769</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34642</t>
+          <t>31761</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>30805</t>
+          <t>31121</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>56990</t>
+          <t>58608</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3362347</t>
+          <t>3362344</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3380746</t>
+          <t>3380405</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3509900</t>
+          <t>3512781</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3532154</t>
+          <t>3531773</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6881902</t>
+          <t>6880284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6908087</t>
+          <t>6907771</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de accidente cerebrovascular en 2023</t>
+          <t>Población con diagnóstico de accidente cerebrovascular en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,97 +6690,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1176</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4435</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6036</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1176</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4882</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6485</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1176</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>7345</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>395552</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>308318</t>
+          <t>307164</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>705842</t>
+          <t>706702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7038,7 +7038,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5351</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7073,7 +7073,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5579</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7108,7 +7108,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -7146,7 +7146,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417138</t>
+          <t>418196</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>505925</t>
+          <t>506155</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>927241</t>
+          <t>927411</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7231,7 +7231,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>4325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7431,7 +7431,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>595</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,7 +7461,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531204</t>
+          <t>532013</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537265</t>
+          <t>536989</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541635</t>
+          <t>541638</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1071839</t>
+          <t>1071865</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1077408</t>
+          <t>1077542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>12411</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1498</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16441</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874422</t>
+          <t>875375</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886489</t>
+          <t>886365</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>704887</t>
+          <t>705199</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>711000</t>
+          <t>711138</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1583844</t>
+          <t>1583631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1595977</t>
+          <t>1596051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8242</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>22146</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4835</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15481</t>
+          <t>14610</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33079</t>
+          <t>31392</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>538142</t>
+          <t>538091</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>552392</t>
+          <t>551995</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>530063</t>
+          <t>529524</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>539138</t>
+          <t>539262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1071254</t>
+          <t>1072941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1088852</t>
+          <t>1089723</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11635</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>13560</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>6534</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21500</t>
+          <t>21870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>354063</t>
+          <t>354249</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362324</t>
+          <t>362269</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>594956</t>
+          <t>594808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>606134</t>
+          <t>605892</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>952565</t>
+          <t>952195</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>967428</t>
+          <t>967531</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20301</t>
+          <t>19915</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>16962</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18936</t>
+          <t>18510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>33506</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>262458</t>
+          <t>262844</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>274552</t>
+          <t>273833</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>408101</t>
+          <t>408710</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>418069</t>
+          <t>417868</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>674841</t>
+          <t>674925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>689495</t>
+          <t>689921</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30398</t>
+          <t>30356</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55342</t>
+          <t>54428</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9111,7 +9111,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25992</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>45340</t>
+          <t>44643</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60051</t>
+          <t>60011</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91572</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3401010</t>
+          <t>3401924</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3425954</t>
+          <t>3425996</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3611797</t>
+          <t>3612494</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3631145</t>
+          <t>3631711</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7021918</t>
+          <t>7020125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7053439</t>
+          <t>7053479</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,7 +9289,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">

--- a/data/trans_orig/P1422-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1422-Edad-trans_orig.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>4171</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,32%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681900</t>
+          <t>681934</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1292163</t>
+          <t>1293171</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3748</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16567</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>15952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>665296</t>
+          <t>665646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>678115</t>
+          <t>678099</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1373575</t>
+          <t>1375485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1387713</t>
+          <t>1388424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10243</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>12315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5094</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18103</t>
+          <t>18248</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>604374</t>
+          <t>604685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>613592</t>
+          <t>613572</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600897</t>
+          <t>601949</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>611319</t>
+          <t>612152</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1210777</t>
+          <t>1210632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1223786</t>
+          <t>1223967</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6972</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2144,7 +2144,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5726</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>933</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>7917</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>422457</t>
+          <t>422372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>442074</t>
+          <t>443053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>867483</t>
+          <t>869312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876289</t>
+          <t>876296</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12655</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13364</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20132</t>
+          <t>20805</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297131</t>
+          <t>298094</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>307756</t>
+          <t>307810</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>340632</t>
+          <t>341503</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>351008</t>
+          <t>350979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>643650</t>
+          <t>642977</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>657704</t>
+          <t>657585</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>23636</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20981</t>
+          <t>20521</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>15916</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>39293</t>
+          <t>38134</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>225157</t>
+          <t>226215</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>243386</t>
+          <t>243516</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>367998</t>
+          <t>368458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>382759</t>
+          <t>383251</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>599537</t>
+          <t>600696</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>622105</t>
+          <t>622914</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>23652</t>
+          <t>22359</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48721</t>
+          <t>48363</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16597</t>
+          <t>16530</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>37842</t>
+          <t>37599</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44325</t>
+          <t>44556</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>76054</t>
+          <t>75941</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3378058</t>
+          <t>3378416</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3403127</t>
+          <t>3404420</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3517256</t>
+          <t>3517499</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3538501</t>
+          <t>3538568</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6905823</t>
+          <t>6905936</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6937552</t>
+          <t>6937321</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4059,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>585575</t>
+          <t>585595</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1148525</t>
+          <t>1149157</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5672</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>6408</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -4510,7 +4510,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>663504</t>
+          <t>663425</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1323993</t>
+          <t>1324075</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1882</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10728</t>
+          <t>12334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2987</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>635320</t>
+          <t>633714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>644166</t>
+          <t>644113</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,7 +4888,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>642039</t>
+          <t>640648</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1281048</t>
+          <t>1280726</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1292138</t>
+          <t>1292090</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7931</t>
+          <t>7978</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6379</t>
+          <t>6359</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10879</t>
+          <t>10091</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>469987</t>
+          <t>469940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5231,7 +5231,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>490470</t>
+          <t>490490</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>963888</t>
+          <t>964676</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>2746</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>14683</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2774</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7726</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24245</t>
+          <t>23328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320081</t>
+          <t>319647</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331522</t>
+          <t>331584</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>362842</t>
+          <t>362982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>374988</t>
+          <t>374945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>687847</t>
+          <t>688764</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>704366</t>
+          <t>705037</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1693</t>
+          <t>2351</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10462</t>
+          <t>9785</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>4469</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19187</t>
+          <t>19662</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>25222</t>
+          <t>23959</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246536</t>
+          <t>247213</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>255305</t>
+          <t>254647</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>380982</t>
+          <t>380507</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>395700</t>
+          <t>395720</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>631945</t>
+          <t>633208</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649255</t>
+          <t>649322</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>13997</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>32006</t>
+          <t>32775</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12769</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31761</t>
+          <t>33118</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>29670</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>58608</t>
+          <t>58871</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3362344</t>
+          <t>3361575</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3380405</t>
+          <t>3380353</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3512781</t>
+          <t>3511424</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3531773</t>
+          <t>3532233</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6880284</t>
+          <t>6880021</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6907771</t>
+          <t>6909222</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -6720,7 +6720,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -6730,12 +6730,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6036</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6755,7 +6755,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1336</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -6765,12 +6765,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -6798,7 +6798,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -6833,27 +6833,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>312024</t>
+          <t>361176</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>307164</t>
+          <t>355469</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6868,27 +6868,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>712011</t>
+          <t>768969</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>706702</t>
+          <t>763679</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6911,17 +6911,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6946,17 +6946,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6981,17 +6981,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7028,7 +7028,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5351</t>
+          <t>7436</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -7053,7 +7053,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>947</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2183</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -7108,12 +7108,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -7141,27 +7141,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>422279</t>
+          <t>475525</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418196</t>
+          <t>469454</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7176,27 +7176,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>510590</t>
+          <t>500136</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>506155</t>
+          <t>495550</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7211,27 +7211,27 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>932868</t>
+          <t>975661</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>927411</t>
+          <t>970637</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>99,77%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7324,17 +7324,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>828</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4325</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -7396,7 +7396,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7406,32 +7406,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4810</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7441,22 +7441,22 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>595</t>
+          <t>739</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -7466,7 +7466,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -7484,27 +7484,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>535493</t>
+          <t>620009</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532013</t>
+          <t>615366</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7519,32 +7519,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>540313</t>
+          <t>619391</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>536989</t>
+          <t>615506</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>541638</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,97%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7554,27 +7554,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1075806</t>
+          <t>1239400</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1071865</t>
+          <t>1235426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1077542</t>
+          <t>1241586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7597,17 +7597,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7632,17 +7632,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>541799</t>
+          <t>621488</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7667,17 +7667,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078137</t>
+          <t>1242325</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7714,32 +7714,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1421</t>
+          <t>2745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12411</t>
+          <t>12891</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7749,32 +7749,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3547</t>
+          <t>3911</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1508</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>8009</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7784,32 +7784,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>9156</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -7827,32 +7827,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>882176</t>
+          <t>694395</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>875375</t>
+          <t>687726</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886365</t>
+          <t>697872</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7862,32 +7862,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>708951</t>
+          <t>732584</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>705199</t>
+          <t>728486</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>711138</t>
+          <t>734987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7897,32 +7897,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1591129</t>
+          <t>1426980</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1583631</t>
+          <t>1419766</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1596051</t>
+          <t>1431839</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -7940,17 +7940,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7975,17 +7975,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712498</t>
+          <t>736495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8010,17 +8010,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600285</t>
+          <t>1437112</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8057,32 +8057,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>13627</t>
+          <t>15093</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8988</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22146</t>
+          <t>24108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8092,32 +8092,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>9741</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4835</t>
+          <t>5518</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14573</t>
+          <t>15843</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8127,32 +8127,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22314</t>
+          <t>24834</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14610</t>
+          <t>17134</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31392</t>
+          <t>35146</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -8170,32 +8170,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>546610</t>
+          <t>593266</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>538091</t>
+          <t>584251</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>551995</t>
+          <t>599371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8205,32 +8205,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>535410</t>
+          <t>596317</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>529524</t>
+          <t>590215</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>539262</t>
+          <t>600540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8240,32 +8240,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1082019</t>
+          <t>1189583</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1072941</t>
+          <t>1179271</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1089723</t>
+          <t>1197283</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,59%</t>
         </is>
       </c>
     </row>
@@ -8283,17 +8283,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560237</t>
+          <t>608359</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8318,17 +8318,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>544097</t>
+          <t>606058</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>544097</t>
+          <t>606058</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>544097</t>
+          <t>606058</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1104333</t>
+          <t>1214417</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1104333</t>
+          <t>1214417</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1104333</t>
+          <t>1214417</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8400,67 +8400,67 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>7029</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>3729</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>12222</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3,02%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7894</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>4138</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>13010</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>7327</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>2476</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>13560</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8470,32 +8470,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14923</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>10222</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21870</t>
+          <t>22181</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -8513,69 +8513,69 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>358988</t>
+          <t>397334</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>354249</t>
+          <t>392141</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>362269</t>
+          <t>400634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>99,08%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>431272</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>426156</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>435028</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>97,04%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>99,06%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>812</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>601041</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>594808</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>605892</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,8%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>97,77%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>99,59%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1368</t>
@@ -8583,32 +8583,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>960027</t>
+          <t>828606</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>952195</t>
+          <t>821348</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>967531</t>
+          <t>833307</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -8626,17 +8626,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>365698</t>
+          <t>404363</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>365698</t>
+          <t>404363</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>365698</t>
+          <t>404363</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974065</t>
+          <t>843529</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974065</t>
+          <t>843529</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974065</t>
+          <t>843529</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8743,32 +8743,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>14302</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19915</t>
+          <t>21336</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8778,32 +8778,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>11659</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7804</t>
+          <t>8421</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8813,32 +8813,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>25205</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18510</t>
+          <t>19912</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33506</t>
+          <t>36873</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -8856,32 +8856,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>269214</t>
+          <t>295896</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>262844</t>
+          <t>288862</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>273833</t>
+          <t>301277</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8891,32 +8891,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>414013</t>
+          <t>451203</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>408710</t>
+          <t>444803</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>417868</t>
+          <t>455517</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8926,32 +8926,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>683226</t>
+          <t>747100</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>674925</t>
+          <t>737264</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>689921</t>
+          <t>754225</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -8969,17 +8969,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9004,17 +9004,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425672</t>
+          <t>463938</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425672</t>
+          <t>463938</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425672</t>
+          <t>463938</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9039,17 +9039,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708431</t>
+          <t>774137</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708431</t>
+          <t>774137</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708431</t>
+          <t>774137</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9086,32 +9086,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>44838</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54428</t>
+          <t>57277</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9121,32 +9121,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>34797</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>30323</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>44643</t>
+          <t>50455</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9156,32 +9156,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>76403</t>
+          <t>83499</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>60011</t>
+          <t>68425</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>93365</t>
+          <t>98810</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -9199,32 +9199,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>3414746</t>
+          <t>3484220</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3401924</t>
+          <t>3471781</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3425996</t>
+          <t>3495090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9234,32 +9234,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3622340</t>
+          <t>3692080</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3612494</t>
+          <t>3680286</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3631711</t>
+          <t>3700418</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9269,32 +9269,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>7037087</t>
+          <t>7176300</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7020125</t>
+          <t>7160989</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>7053479</t>
+          <t>7191374</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -9312,17 +9312,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3456352</t>
+          <t>3529058</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3456352</t>
+          <t>3529058</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3456352</t>
+          <t>3529058</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9347,17 +9347,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3657137</t>
+          <t>3730741</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3657137</t>
+          <t>3730741</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3657137</t>
+          <t>3730741</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9382,17 +9382,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7113490</t>
+          <t>7259799</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7113490</t>
+          <t>7259799</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7113490</t>
+          <t>7259799</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
